--- a/outputs/evaluation/requirement/design/v1/CF_M05/CF_M05_req_eval_avg.xlsx
+++ b/outputs/evaluation/requirement/design/v1/CF_M05/CF_M05_req_eval_avg.xlsx
@@ -455,7 +455,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.3333</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
@@ -465,7 +465,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.6667</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -475,7 +475,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2.6667</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -485,7 +485,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8147</v>
+        <v>0.8359</v>
       </c>
     </row>
     <row r="8">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8975</v>
+        <v>0.9231</v>
       </c>
     </row>
     <row r="9">
@@ -542,16 +542,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8147</v>
+        <v>0.8359</v>
       </c>
       <c r="C13" t="n">
-        <v>0.9333</v>
+        <v>0.9231</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8661</v>
+        <v>0.8735000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9475</v>
+        <v>0.9471000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -583,7 +583,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.899</v>
+        <v>0.9012</v>
       </c>
     </row>
     <row r="19">
@@ -624,10 +624,8 @@
           <t>fixes</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" t="n">
+        <v>0.7073</v>
       </c>
     </row>
   </sheetData>
